--- a/output/yearly_benthic_cover_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_74_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.56438089527404</v>
+        <v>45.11402747207241</v>
       </c>
       <c r="M2" t="n">
-        <v>98.66309417973693</v>
+        <v>99.6549768748246</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10421370625532</v>
+        <v>87.90642099628073</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9468672907168</v>
+        <v>45.83736328813895</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228913958216167</v>
+        <v>2.228489465260083</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721004027556715</v>
+        <v>5.64772128066841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429713194053892</v>
+        <v>0.742829821753361</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97861646173195</v>
+        <v>33.94265993353353</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1766806926479</v>
+        <v>34.1701718006546</v>
       </c>
       <c r="I3" t="n">
-        <v>6.612456500413513</v>
+        <v>6.531862308452228</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643570746283682</v>
+        <v>4.642686385958506</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89578629374468</v>
+        <v>12.09357900371928</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92001266019857</v>
+        <v>48.83457197562106</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7626662446601</v>
+        <v>106.7655142674793</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.31465453130313</v>
+        <v>86.93526754090276</v>
       </c>
       <c r="C4" t="n">
-        <v>42.80034332812658</v>
+        <v>42.49775014423358</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191551376929058</v>
+        <v>2.181290104617592</v>
       </c>
       <c r="E4" t="n">
-        <v>6.545437435384018</v>
+        <v>6.437203122403004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445375647810831</v>
+        <v>0.7443834074331894</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40904363686121</v>
+        <v>33.22375510030772</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24872797992982</v>
+        <v>34.24163674192671</v>
       </c>
       <c r="I4" t="n">
-        <v>5.521996757536176</v>
+        <v>5.454602767757114</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65335977988177</v>
+        <v>4.652396296457434</v>
       </c>
       <c r="K4" t="n">
-        <v>12.68534546869686</v>
+        <v>13.06473245909722</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33063185594284</v>
+        <v>44.25607677698996</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81632065276628</v>
+        <v>99.81855938032078</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.30460659860026</v>
+        <v>85.73825409490635</v>
       </c>
       <c r="C5" t="n">
-        <v>42.64746607535471</v>
+        <v>42.14720200650914</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142838355628332</v>
+        <v>2.122639388285422</v>
       </c>
       <c r="E5" t="n">
-        <v>7.168257296972633</v>
+        <v>7.023043940747675</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458631841472991</v>
+        <v>0.7457012114918139</v>
       </c>
       <c r="G5" t="n">
-        <v>32.66643934683547</v>
+        <v>32.33043190970935</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30970647077576</v>
+        <v>34.30225572862344</v>
       </c>
       <c r="I5" t="n">
-        <v>4.609857043320131</v>
+        <v>4.553549344224817</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66164490092062</v>
+        <v>4.660632571823837</v>
       </c>
       <c r="K5" t="n">
-        <v>13.69539340139976</v>
+        <v>14.26174590509363</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50375172442507</v>
+        <v>43.43953534484841</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84661120117954</v>
+        <v>99.84848325645119</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.05437240970969</v>
+        <v>84.27369675660483</v>
       </c>
       <c r="C6" t="n">
-        <v>42.11342191737653</v>
+        <v>41.38969652085284</v>
       </c>
       <c r="D6" t="n">
-        <v>2.08215205403432</v>
+        <v>2.050765183977416</v>
       </c>
       <c r="E6" t="n">
-        <v>7.606471806964152</v>
+        <v>7.418626333814967</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469877938283689</v>
+        <v>0.7468221264837401</v>
       </c>
       <c r="G6" t="n">
-        <v>31.741308720441</v>
+        <v>31.23569858794547</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36143851610497</v>
+        <v>34.35381781825205</v>
       </c>
       <c r="I6" t="n">
-        <v>3.847339806909571</v>
+        <v>3.800328415607817</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668673711427306</v>
+        <v>4.667638290523376</v>
       </c>
       <c r="K6" t="n">
-        <v>14.94562759029031</v>
+        <v>15.72630324339516</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81289890779649</v>
+        <v>42.75751275396796</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87194841546332</v>
+        <v>99.87351251821596</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.47972834083861</v>
+        <v>82.72820945497278</v>
       </c>
       <c r="C7" t="n">
-        <v>41.1366290573564</v>
+        <v>40.43424832164617</v>
       </c>
       <c r="D7" t="n">
-        <v>2.005582407419729</v>
+        <v>1.97542263325109</v>
       </c>
       <c r="E7" t="n">
-        <v>7.861786973354551</v>
+        <v>7.674573047275603</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479453116420627</v>
+        <v>0.7477763205509523</v>
       </c>
       <c r="G7" t="n">
-        <v>30.57404488536244</v>
+        <v>30.08813804628942</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40548433553488</v>
+        <v>34.39771074534381</v>
       </c>
       <c r="I7" t="n">
-        <v>3.210226229762042</v>
+        <v>3.170986658818457</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674658197762891</v>
+        <v>4.673602003443452</v>
       </c>
       <c r="K7" t="n">
-        <v>16.52027165916142</v>
+        <v>17.27179054502723</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23622873329025</v>
+        <v>42.18839645511527</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89312944980807</v>
+        <v>99.89443532178866</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.19283671896085</v>
+        <v>87.71494012779705</v>
       </c>
       <c r="C8" t="n">
-        <v>43.42060218155814</v>
+        <v>42.75400394676682</v>
       </c>
       <c r="D8" t="n">
-        <v>2.009766704897355</v>
+        <v>1.979710625354115</v>
       </c>
       <c r="E8" t="n">
-        <v>9.675452609534778</v>
+        <v>9.523910564253288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495057689283491</v>
+        <v>0.7493994967277255</v>
       </c>
       <c r="G8" t="n">
-        <v>31.07646660252973</v>
+        <v>30.59378812568461</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47726537070405</v>
+        <v>34.47237684947537</v>
       </c>
       <c r="I8" t="n">
-        <v>5.519968606564393</v>
+        <v>5.712007611753644</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684411055802181</v>
+        <v>4.683746854548285</v>
       </c>
       <c r="K8" t="n">
-        <v>11.80716328103916</v>
+        <v>12.28505987220295</v>
       </c>
       <c r="L8" t="n">
-        <v>44.58861866630255</v>
+        <v>44.77094832837724</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81638412889984</v>
+        <v>99.81001214734701</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.07562920263005</v>
+        <v>85.78851206318951</v>
       </c>
       <c r="C9" t="n">
-        <v>42.16064647602671</v>
+        <v>41.71371513793353</v>
       </c>
       <c r="D9" t="n">
-        <v>1.913668512254659</v>
+        <v>1.892617104851799</v>
       </c>
       <c r="E9" t="n">
-        <v>9.980845529412093</v>
+        <v>9.899729023731659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508432979360919</v>
+        <v>0.7507880882677627</v>
       </c>
       <c r="G9" t="n">
-        <v>29.5905268330296</v>
+        <v>29.24787388991533</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53879170506023</v>
+        <v>34.53625206031708</v>
       </c>
       <c r="I9" t="n">
-        <v>4.608182712836818</v>
+        <v>4.768826344432351</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692770612100574</v>
+        <v>4.692425551673517</v>
       </c>
       <c r="K9" t="n">
-        <v>13.92437079736994</v>
+        <v>14.2114879368105</v>
       </c>
       <c r="L9" t="n">
-        <v>43.7616502653099</v>
+        <v>43.91613004715169</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84666753870654</v>
+        <v>99.84133312189573</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.80031274156968</v>
+        <v>83.61659745109023</v>
       </c>
       <c r="C10" t="n">
-        <v>40.60059308835496</v>
+        <v>40.28143048694953</v>
       </c>
       <c r="D10" t="n">
-        <v>1.811477195128776</v>
+        <v>1.795300914539316</v>
       </c>
       <c r="E10" t="n">
-        <v>10.08886549142404</v>
+        <v>10.0540843138677</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751991966541202</v>
+        <v>0.7519793918698032</v>
       </c>
       <c r="G10" t="n">
-        <v>28.01037076516737</v>
+        <v>27.7439819223272</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59163046089529</v>
+        <v>34.59105202601095</v>
       </c>
       <c r="I10" t="n">
-        <v>3.846027071530489</v>
+        <v>3.980327683288972</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699949790882513</v>
+        <v>4.69987119918627</v>
       </c>
       <c r="K10" t="n">
-        <v>16.19968725843032</v>
+        <v>16.38340254890979</v>
       </c>
       <c r="L10" t="n">
-        <v>43.07171457785815</v>
+        <v>43.20269956568422</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87199492464342</v>
+        <v>99.86753260154354</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.32517842795573</v>
+        <v>81.30907745360845</v>
       </c>
       <c r="C11" t="n">
-        <v>38.7217415312489</v>
+        <v>38.59064983446797</v>
       </c>
       <c r="D11" t="n">
-        <v>1.701370226750345</v>
+        <v>1.692972051021625</v>
       </c>
       <c r="E11" t="n">
-        <v>10.0105073295084</v>
+        <v>10.03459597089367</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529811319146638</v>
+        <v>0.753003331118492</v>
       </c>
       <c r="G11" t="n">
-        <v>26.30781717166814</v>
+        <v>26.16262577385355</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63713206807453</v>
+        <v>34.63815323145064</v>
       </c>
       <c r="I11" t="n">
-        <v>3.209238425572988</v>
+        <v>3.321456275779915</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706132074466648</v>
+        <v>4.706270819490576</v>
       </c>
       <c r="K11" t="n">
-        <v>18.67482157204427</v>
+        <v>18.69092254639153</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49660281138654</v>
+        <v>42.60786296127136</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89316591467971</v>
+        <v>99.88943534213087</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.84503842791442</v>
+        <v>79.02174194887699</v>
       </c>
       <c r="C12" t="n">
-        <v>36.73826341890761</v>
+        <v>36.81717499379196</v>
       </c>
       <c r="D12" t="n">
-        <v>1.592184877731291</v>
+        <v>1.59263108844894</v>
       </c>
       <c r="E12" t="n">
-        <v>9.814315611269473</v>
+        <v>9.901706917081253</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538334476704887</v>
+        <v>0.7538835358499161</v>
       </c>
       <c r="G12" t="n">
-        <v>24.61951432337835</v>
+        <v>24.61198998397549</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67633859284248</v>
+        <v>34.67864264909615</v>
       </c>
       <c r="I12" t="n">
-        <v>2.677392527081797</v>
+        <v>2.771115675363272</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711459047940554</v>
+        <v>4.711772099061976</v>
       </c>
       <c r="K12" t="n">
-        <v>21.15496157208556</v>
+        <v>20.978258051123</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01762949718534</v>
+        <v>42.11230428075781</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91085448817853</v>
+        <v>99.90773732567278</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.36548024050693</v>
+        <v>76.65666922082269</v>
       </c>
       <c r="C13" t="n">
-        <v>34.67215014584788</v>
+        <v>34.88001597443508</v>
       </c>
       <c r="D13" t="n">
-        <v>1.484045065841685</v>
+        <v>1.489804977663625</v>
       </c>
       <c r="E13" t="n">
-        <v>9.519958411388931</v>
+        <v>9.647680405341632</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545683185291105</v>
+        <v>0.7546413152371743</v>
       </c>
       <c r="G13" t="n">
-        <v>22.94737832649765</v>
+        <v>23.02294954197079</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71014265233909</v>
+        <v>34.71350050091002</v>
       </c>
       <c r="I13" t="n">
-        <v>2.233335475103523</v>
+        <v>2.31158425946711</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716051990806942</v>
+        <v>4.71650822023234</v>
       </c>
       <c r="K13" t="n">
-        <v>23.63451975949309</v>
+        <v>23.34333077917731</v>
       </c>
       <c r="L13" t="n">
-        <v>41.61895808001786</v>
+        <v>41.69967781096085</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92562798535883</v>
+        <v>99.92302456457324</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.36647444891828</v>
+        <v>83.40714825630523</v>
       </c>
       <c r="C14" t="n">
-        <v>39.05950068360198</v>
+        <v>39.09833730107715</v>
       </c>
       <c r="D14" t="n">
-        <v>1.485735945265256</v>
+        <v>1.491553835570297</v>
       </c>
       <c r="E14" t="n">
-        <v>11.94752419400952</v>
+        <v>11.99786726984185</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554280525579798</v>
+        <v>0.7555271764409162</v>
       </c>
       <c r="G14" t="n">
-        <v>24.91531579394046</v>
+        <v>24.89928592341751</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69148228432574</v>
+        <v>36.60356023056971</v>
       </c>
       <c r="I14" t="n">
-        <v>2.849562850331951</v>
+        <v>2.937308967709213</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721425328487375</v>
+        <v>4.722044852755727</v>
       </c>
       <c r="K14" t="n">
-        <v>16.63352555108173</v>
+        <v>16.59285174369479</v>
       </c>
       <c r="L14" t="n">
-        <v>44.21209643754443</v>
+        <v>44.21101545685426</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90512267222815</v>
+        <v>99.90220450162619</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.53380513356134</v>
+        <v>82.65313656701255</v>
       </c>
       <c r="C15" t="n">
-        <v>38.66710728851794</v>
+        <v>38.79818209482639</v>
       </c>
       <c r="D15" t="n">
-        <v>1.454871204296975</v>
+        <v>1.463702394047762</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09547837478066</v>
+        <v>12.182196553758</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561532457058172</v>
+        <v>0.7562737400422422</v>
       </c>
       <c r="G15" t="n">
-        <v>24.39772397651586</v>
+        <v>24.43434728740523</v>
       </c>
       <c r="H15" t="n">
-        <v>36.72670524360888</v>
+        <v>36.63972952612811</v>
       </c>
       <c r="I15" t="n">
-        <v>2.376915302991797</v>
+        <v>2.450176190367194</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725957785661359</v>
+        <v>4.726710875264015</v>
       </c>
       <c r="K15" t="n">
-        <v>17.46619486643867</v>
+        <v>17.34686343298746</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78754332142307</v>
+        <v>43.77336255641645</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92084547637968</v>
+        <v>99.91840808423031</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.08783963329269</v>
+        <v>80.24921932091675</v>
       </c>
       <c r="C16" t="n">
-        <v>36.58838842644616</v>
+        <v>36.77290497781956</v>
       </c>
       <c r="D16" t="n">
-        <v>1.362219652366561</v>
+        <v>1.3724662784909</v>
       </c>
       <c r="E16" t="n">
-        <v>11.65559331382514</v>
+        <v>11.76344184380658</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567771423266287</v>
+        <v>0.7569156904903616</v>
       </c>
       <c r="G16" t="n">
-        <v>22.84398713485063</v>
+        <v>22.91129523684101</v>
       </c>
       <c r="H16" t="n">
-        <v>36.75700818474568</v>
+        <v>36.67083055415925</v>
       </c>
       <c r="I16" t="n">
-        <v>1.982397065636602</v>
+        <v>2.04354665156389</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729857139541431</v>
+        <v>4.73072306556476</v>
       </c>
       <c r="K16" t="n">
-        <v>19.91216036670734</v>
+        <v>19.75078067908325</v>
       </c>
       <c r="L16" t="n">
-        <v>43.4334257817634</v>
+        <v>43.40825389336479</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93397457491689</v>
+        <v>99.9319395502676</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.80284488036438</v>
+        <v>81.91571641392161</v>
       </c>
       <c r="C17" t="n">
-        <v>37.83327418876013</v>
+        <v>37.99028619630754</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3633163004635</v>
+        <v>1.373602294979837</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43745143095707</v>
+        <v>12.53626114680206</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573863819683396</v>
+        <v>0.7575422040292424</v>
       </c>
       <c r="G17" t="n">
-        <v>23.30557756294893</v>
+        <v>23.35432583422745</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22979922063914</v>
+        <v>37.12525018109456</v>
       </c>
       <c r="I17" t="n">
-        <v>1.975649096085259</v>
+        <v>2.034095977605722</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733664887302123</v>
+        <v>4.734638775182765</v>
       </c>
       <c r="K17" t="n">
-        <v>18.19715511963563</v>
+        <v>18.08428358607837</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90376869530174</v>
+        <v>43.85768309394563</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9341980036975</v>
+        <v>99.93225287633155</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.48000035968529</v>
+        <v>79.56163268129343</v>
       </c>
       <c r="C18" t="n">
-        <v>35.81528286344837</v>
+        <v>35.95016107763339</v>
       </c>
       <c r="D18" t="n">
-        <v>1.278856187725699</v>
+        <v>1.287742493671725</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9415122782277</v>
+        <v>12.03537078865347</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579097014651516</v>
+        <v>0.7580805737440111</v>
       </c>
       <c r="G18" t="n">
-        <v>21.86175142537762</v>
+        <v>21.89451626406281</v>
       </c>
       <c r="H18" t="n">
-        <v>37.25552331636941</v>
+        <v>37.15163433532967</v>
       </c>
       <c r="I18" t="n">
-        <v>1.647511816362519</v>
+        <v>1.696284639931655</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736935634157198</v>
+        <v>4.738003585900069</v>
       </c>
       <c r="K18" t="n">
-        <v>20.51999964031471</v>
+        <v>20.43836731870658</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60983835467898</v>
+        <v>43.55496893761543</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94512085844207</v>
+        <v>99.94349733395541</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.58549075643784</v>
+        <v>78.61743682673405</v>
       </c>
       <c r="C19" t="n">
-        <v>35.17138219665712</v>
+        <v>35.26548619824769</v>
       </c>
       <c r="D19" t="n">
-        <v>1.24685079329499</v>
+        <v>1.253901139007007</v>
       </c>
       <c r="E19" t="n">
-        <v>11.87208929943505</v>
+        <v>11.95508457636201</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583522485510731</v>
+        <v>0.7585357040001128</v>
       </c>
       <c r="G19" t="n">
-        <v>21.31462659302281</v>
+        <v>21.31913718498005</v>
       </c>
       <c r="H19" t="n">
-        <v>37.27727699394639</v>
+        <v>37.17393913172635</v>
       </c>
       <c r="I19" t="n">
-        <v>1.376593274743313</v>
+        <v>1.415990940657816</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739701553444207</v>
+        <v>4.740848150000705</v>
       </c>
       <c r="K19" t="n">
-        <v>21.41450924356215</v>
+        <v>21.38256317326595</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36824889496609</v>
+        <v>43.30477925083291</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95414033518537</v>
+        <v>99.95282862234654</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.03537164222564</v>
+        <v>76.10759882082708</v>
       </c>
       <c r="C20" t="n">
-        <v>32.83299333047272</v>
+        <v>32.97348600686691</v>
       </c>
       <c r="D20" t="n">
-        <v>1.155091043161354</v>
+        <v>1.163356706735526</v>
       </c>
       <c r="E20" t="n">
-        <v>11.18967387009025</v>
+        <v>11.28857281585588</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587338209154414</v>
+        <v>0.7589279246786899</v>
       </c>
       <c r="G20" t="n">
-        <v>19.74601483860513</v>
+        <v>19.77967836092912</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29603342111724</v>
+        <v>37.19316088695124</v>
       </c>
       <c r="I20" t="n">
-        <v>1.147738267614731</v>
+        <v>1.180602596434826</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742086380721509</v>
+        <v>4.743299529241812</v>
       </c>
       <c r="K20" t="n">
-        <v>23.96462835777436</v>
+        <v>23.89240117917292</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1641396096767</v>
+        <v>43.09477973227523</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96176129792377</v>
+        <v>99.96066691831506</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.96285012120251</v>
+        <v>81.82319651027339</v>
       </c>
       <c r="C21" t="n">
-        <v>36.54665415378065</v>
+        <v>36.54351019274363</v>
       </c>
       <c r="D21" t="n">
-        <v>1.155847858473613</v>
+        <v>1.164138838727751</v>
       </c>
       <c r="E21" t="n">
-        <v>13.18104190266224</v>
+        <v>13.21136934701732</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592309430920849</v>
+        <v>0.7594381566705181</v>
       </c>
       <c r="G21" t="n">
-        <v>21.47447880662147</v>
+        <v>21.43313228085712</v>
       </c>
       <c r="H21" t="n">
-        <v>39.03599615615486</v>
+        <v>38.85832200012513</v>
       </c>
       <c r="I21" t="n">
-        <v>1.611061059872713</v>
+        <v>1.650307407684836</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745193394325531</v>
+        <v>4.746488479190738</v>
       </c>
       <c r="K21" t="n">
-        <v>18.03714987879748</v>
+        <v>18.17680348972659</v>
       </c>
       <c r="L21" t="n">
-        <v>45.3625290946121</v>
+        <v>45.22471302949244</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94633312719023</v>
+        <v>99.94502671196267</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_74_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.11402747207241</v>
+        <v>45.58973163371944</v>
       </c>
       <c r="M2" t="n">
-        <v>99.6549768748246</v>
+        <v>98.91143993348561</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.90642099628073</v>
+        <v>88.06061429070972</v>
       </c>
       <c r="C3" t="n">
-        <v>45.83736328813895</v>
+        <v>45.94945385503286</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228489465260083</v>
+        <v>2.228800274374576</v>
       </c>
       <c r="E3" t="n">
-        <v>5.64772128066841</v>
+        <v>5.72000761511196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742829821753361</v>
+        <v>0.7429334247915254</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94265993353353</v>
+        <v>33.9799900854966</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1701718006546</v>
+        <v>34.17493754041016</v>
       </c>
       <c r="I3" t="n">
-        <v>6.531862308452228</v>
+        <v>6.570611445577874</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642686385958506</v>
+        <v>4.643333904947033</v>
       </c>
       <c r="K3" t="n">
-        <v>12.09357900371928</v>
+        <v>11.93938570929028</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83457197562106</v>
+        <v>48.87531655065502</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655142674793</v>
+        <v>106.7641561149782</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.93526754090276</v>
+        <v>87.20985155342159</v>
       </c>
       <c r="C4" t="n">
-        <v>42.49775014423358</v>
+        <v>42.73355358548342</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181290104617592</v>
+        <v>2.188155937218148</v>
       </c>
       <c r="E4" t="n">
-        <v>6.437203122403004</v>
+        <v>6.530196552420548</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443834074331894</v>
+        <v>0.7444915325874595</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22375510030772</v>
+        <v>33.36033197189798</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24163674192671</v>
+        <v>34.24661049902313</v>
       </c>
       <c r="I4" t="n">
-        <v>5.454602767757114</v>
+        <v>5.486992981602683</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652396296457434</v>
+        <v>4.653072078671621</v>
       </c>
       <c r="K4" t="n">
-        <v>13.06473245909722</v>
+        <v>12.79014844657844</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25607677698996</v>
+        <v>44.29378098333876</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81855938032078</v>
+        <v>99.81748301540061</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.73825409490635</v>
+        <v>86.10665498429458</v>
       </c>
       <c r="C5" t="n">
-        <v>42.14720200650914</v>
+        <v>42.48206178355309</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122639388285422</v>
+        <v>2.134566401878913</v>
       </c>
       <c r="E5" t="n">
-        <v>7.023043940747675</v>
+        <v>7.133700978959683</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457012114918139</v>
+        <v>0.7458116858990289</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33043190970935</v>
+        <v>32.54331310284543</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30225572862344</v>
+        <v>34.30733755135533</v>
       </c>
       <c r="I5" t="n">
-        <v>4.553549344224817</v>
+        <v>4.580602226487262</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660632571823837</v>
+        <v>4.66132303686893</v>
       </c>
       <c r="K5" t="n">
-        <v>14.26174590509363</v>
+        <v>13.89334501570543</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43953534484841</v>
+        <v>43.47217672903032</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84848325645119</v>
+        <v>99.84758352828884</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.27369675660483</v>
+        <v>84.78898533084809</v>
       </c>
       <c r="C6" t="n">
-        <v>41.38969652085284</v>
+        <v>41.87591726981537</v>
       </c>
       <c r="D6" t="n">
-        <v>2.050765183977416</v>
+        <v>2.07040364047598</v>
       </c>
       <c r="E6" t="n">
-        <v>7.418626333814967</v>
+        <v>7.556420526485976</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468221264837401</v>
+        <v>0.7469325734358179</v>
       </c>
       <c r="G6" t="n">
-        <v>31.23569858794547</v>
+        <v>31.56509624716887</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35381781825205</v>
+        <v>34.35889837804762</v>
       </c>
       <c r="I6" t="n">
-        <v>3.800328415607817</v>
+        <v>3.822905381259976</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667638290523376</v>
+        <v>4.668328583973861</v>
       </c>
       <c r="K6" t="n">
-        <v>15.72630324339516</v>
+        <v>15.2110146691519</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75751275396796</v>
+        <v>42.78582911029698</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87351251821596</v>
+        <v>99.87276104926426</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.72820945497278</v>
+        <v>83.37791365670429</v>
       </c>
       <c r="C7" t="n">
-        <v>40.43424832164617</v>
+        <v>41.05874039415338</v>
       </c>
       <c r="D7" t="n">
-        <v>1.97542263325109</v>
+        <v>2.002029656536116</v>
       </c>
       <c r="E7" t="n">
-        <v>7.674573047275603</v>
+        <v>7.838509923200354</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477763205509523</v>
+        <v>0.7478850951894056</v>
       </c>
       <c r="G7" t="n">
-        <v>30.08813804628942</v>
+        <v>30.5226756574485</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39771074534381</v>
+        <v>34.40271437871265</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170986658818457</v>
+        <v>3.189817100683479</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673602003443452</v>
+        <v>4.674281844933784</v>
       </c>
       <c r="K7" t="n">
-        <v>17.27179054502723</v>
+        <v>16.62208634329572</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18839645511527</v>
+        <v>42.2129814464048</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89443532178866</v>
+        <v>99.89380818385389</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.71494012779705</v>
+        <v>88.37096244791047</v>
       </c>
       <c r="C8" t="n">
-        <v>42.75400394676682</v>
+        <v>43.37239346210924</v>
       </c>
       <c r="D8" t="n">
-        <v>1.979710625354115</v>
+        <v>2.00636652314173</v>
       </c>
       <c r="E8" t="n">
-        <v>9.523910564253288</v>
+        <v>9.685338170442714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493994967277255</v>
+        <v>0.7495051900184577</v>
       </c>
       <c r="G8" t="n">
-        <v>30.59378812568461</v>
+        <v>31.02513837293072</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47237684947537</v>
+        <v>34.47723874084905</v>
       </c>
       <c r="I8" t="n">
-        <v>5.712007611753644</v>
+        <v>5.742968012912427</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683746854548285</v>
+        <v>4.68440743761536</v>
       </c>
       <c r="K8" t="n">
-        <v>12.28505987220295</v>
+        <v>11.62903755208954</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77094832837724</v>
+        <v>44.80755050960268</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81001214734701</v>
+        <v>99.80898152380146</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.78851206318951</v>
+        <v>86.56896786540942</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71371513793353</v>
+        <v>42.46198812027041</v>
       </c>
       <c r="D9" t="n">
-        <v>1.892617104851799</v>
+        <v>1.925276522765515</v>
       </c>
       <c r="E9" t="n">
-        <v>9.899729023731659</v>
+        <v>10.09299922584513</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507880882677627</v>
+        <v>0.7508889072383336</v>
       </c>
       <c r="G9" t="n">
-        <v>29.24787388991533</v>
+        <v>29.77121569563566</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53625206031708</v>
+        <v>34.54088973296334</v>
       </c>
       <c r="I9" t="n">
-        <v>4.768826344432351</v>
+        <v>4.794642110721873</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692425551673517</v>
+        <v>4.693055670239584</v>
       </c>
       <c r="K9" t="n">
-        <v>14.2114879368105</v>
+        <v>13.43103213459058</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91613004715169</v>
+        <v>43.94745285589144</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84133312189573</v>
+        <v>99.84047311075243</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.61659745109023</v>
+        <v>84.59574166264551</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28143048694953</v>
+        <v>41.23307666409875</v>
       </c>
       <c r="D10" t="n">
-        <v>1.795300914539316</v>
+        <v>1.837260873057303</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0540843138677</v>
+        <v>10.2985617760797</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519793918698032</v>
+        <v>0.7520729439208435</v>
       </c>
       <c r="G10" t="n">
-        <v>27.7439819223272</v>
+        <v>28.41019931119921</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59105202601095</v>
+        <v>34.59535542035879</v>
       </c>
       <c r="I10" t="n">
-        <v>3.980327683288972</v>
+        <v>4.001835438524374</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69987119918627</v>
+        <v>4.70045589950527</v>
       </c>
       <c r="K10" t="n">
-        <v>16.38340254890979</v>
+        <v>15.4042583373545</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20269956568422</v>
+        <v>43.22948049547115</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86753260154354</v>
+        <v>99.8668154969244</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.30907745360845</v>
+        <v>82.44975981595643</v>
       </c>
       <c r="C11" t="n">
-        <v>38.59064983446797</v>
+        <v>39.70792353514082</v>
       </c>
       <c r="D11" t="n">
-        <v>1.692972051021625</v>
+        <v>1.74236918411664</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03459597089367</v>
+        <v>10.32321780787109</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753003331118492</v>
+        <v>0.7530882879604626</v>
       </c>
       <c r="G11" t="n">
-        <v>26.16262577385355</v>
+        <v>26.94285635772171</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63815323145064</v>
+        <v>34.64206124618127</v>
       </c>
       <c r="I11" t="n">
-        <v>3.321456275779915</v>
+        <v>3.33936513235236</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706270819490576</v>
+        <v>4.706801799752889</v>
       </c>
       <c r="K11" t="n">
-        <v>18.69092254639153</v>
+        <v>17.55024018404357</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60786296127136</v>
+        <v>42.63067418530105</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88943534213087</v>
+        <v>99.88883790448544</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.02174194887699</v>
+        <v>80.06965951090092</v>
       </c>
       <c r="C12" t="n">
-        <v>36.81717499379196</v>
+        <v>37.84523204544111</v>
       </c>
       <c r="D12" t="n">
-        <v>1.59263108844894</v>
+        <v>1.637956083067075</v>
       </c>
       <c r="E12" t="n">
-        <v>9.901706917081253</v>
+        <v>10.16892798287378</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538835358499161</v>
+        <v>0.7539617473907135</v>
       </c>
       <c r="G12" t="n">
-        <v>24.61198998397549</v>
+        <v>25.32828052093144</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67864264909615</v>
+        <v>34.68224037997282</v>
       </c>
       <c r="I12" t="n">
-        <v>2.771115675363272</v>
+        <v>2.786031875473134</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711772099061976</v>
+        <v>4.712260921191958</v>
       </c>
       <c r="K12" t="n">
-        <v>20.978258051123</v>
+        <v>19.93034048909908</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11230428075781</v>
+        <v>42.13166732289446</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90773732567278</v>
+        <v>99.90723985743465</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.65666922082269</v>
+        <v>77.67692016506126</v>
       </c>
       <c r="C13" t="n">
-        <v>34.88001597443508</v>
+        <v>35.88333586001684</v>
       </c>
       <c r="D13" t="n">
-        <v>1.489804977663625</v>
+        <v>1.533945524215433</v>
       </c>
       <c r="E13" t="n">
-        <v>9.647680405341632</v>
+        <v>9.910533672618266</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546413152371743</v>
+        <v>0.7547136711353766</v>
       </c>
       <c r="G13" t="n">
-        <v>23.02294954197079</v>
+        <v>23.71992933315094</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71350050091002</v>
+        <v>34.71682887222732</v>
       </c>
       <c r="I13" t="n">
-        <v>2.31158425946711</v>
+        <v>2.324008647117833</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71650822023234</v>
+        <v>4.716960444596102</v>
       </c>
       <c r="K13" t="n">
-        <v>23.34333077917731</v>
+        <v>22.32307983493873</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69967781096085</v>
+        <v>41.71619453072572</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92302456457324</v>
+        <v>99.9226102256813</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.40714825630523</v>
+        <v>84.18329835632866</v>
       </c>
       <c r="C14" t="n">
-        <v>39.09833730107715</v>
+        <v>39.76899256506196</v>
       </c>
       <c r="D14" t="n">
-        <v>1.491553835570297</v>
+        <v>1.535901603431192</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99786726984185</v>
+        <v>12.11893662338747</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555271764409162</v>
+        <v>0.755676078015316</v>
       </c>
       <c r="G14" t="n">
-        <v>24.89928592341751</v>
+        <v>25.40919146911327</v>
       </c>
       <c r="H14" t="n">
-        <v>36.60356023056971</v>
+        <v>36.42011419629289</v>
       </c>
       <c r="I14" t="n">
-        <v>2.937308967709213</v>
+        <v>3.220502898492804</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722044852755727</v>
+        <v>4.722975487595723</v>
       </c>
       <c r="K14" t="n">
-        <v>16.59285174369479</v>
+        <v>15.81670164367134</v>
       </c>
       <c r="L14" t="n">
-        <v>44.21101545685426</v>
+        <v>44.30709241258347</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90220450162619</v>
+        <v>99.89278662131676</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.65313656701255</v>
+        <v>83.41525749234228</v>
       </c>
       <c r="C15" t="n">
-        <v>38.79818209482639</v>
+        <v>39.49005580001082</v>
       </c>
       <c r="D15" t="n">
-        <v>1.463702394047762</v>
+        <v>1.506269601344428</v>
       </c>
       <c r="E15" t="n">
-        <v>12.182196553758</v>
+        <v>12.34181015992635</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562737400422422</v>
+        <v>0.7564873703649724</v>
       </c>
       <c r="G15" t="n">
-        <v>24.43434728740523</v>
+        <v>24.92788511453782</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63972952612811</v>
+        <v>36.46812549466731</v>
       </c>
       <c r="I15" t="n">
-        <v>2.450176190367194</v>
+        <v>2.686633686720347</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726710875264015</v>
+        <v>4.728046064781075</v>
       </c>
       <c r="K15" t="n">
-        <v>17.34686343298746</v>
+        <v>16.58474250765771</v>
       </c>
       <c r="L15" t="n">
-        <v>43.77336255641645</v>
+        <v>43.83574327848446</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91840808423031</v>
+        <v>99.91054158615299</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.24921932091675</v>
+        <v>80.9741418257326</v>
       </c>
       <c r="C16" t="n">
-        <v>36.77290497781956</v>
+        <v>37.46448014716393</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3724662784909</v>
+        <v>1.412745415125774</v>
       </c>
       <c r="E16" t="n">
-        <v>11.76344184380658</v>
+        <v>11.94899571932394</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569156904903616</v>
+        <v>0.7571852197966021</v>
       </c>
       <c r="G16" t="n">
-        <v>22.91129523684101</v>
+        <v>23.38011427231383</v>
       </c>
       <c r="H16" t="n">
-        <v>36.67083055415925</v>
+        <v>36.50176685028806</v>
       </c>
       <c r="I16" t="n">
-        <v>2.04354665156389</v>
+        <v>2.240926725155647</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73072306556476</v>
+        <v>4.73240762372876</v>
       </c>
       <c r="K16" t="n">
-        <v>19.75078067908325</v>
+        <v>19.0258581742674</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40825389336479</v>
+        <v>43.43503296504867</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9319395502676</v>
+        <v>99.92537128647999</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.91571641392161</v>
+        <v>82.63006549596273</v>
       </c>
       <c r="C17" t="n">
-        <v>37.99028619630754</v>
+        <v>38.65324011704205</v>
       </c>
       <c r="D17" t="n">
-        <v>1.373602294979837</v>
+        <v>1.414045731244722</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53626114680206</v>
+        <v>12.727760177807</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575422040292424</v>
+        <v>0.7578821466001077</v>
       </c>
       <c r="G17" t="n">
-        <v>23.35432583422745</v>
+        <v>23.78912919413871</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12525018109456</v>
+        <v>36.9228591755656</v>
       </c>
       <c r="I17" t="n">
-        <v>2.034095977605722</v>
+        <v>2.28162565435592</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734638775182765</v>
+        <v>4.73676341625067</v>
       </c>
       <c r="K17" t="n">
-        <v>18.08428358607837</v>
+        <v>17.36993450403726</v>
       </c>
       <c r="L17" t="n">
-        <v>43.85768309394563</v>
+        <v>43.90084112770447</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93225287633155</v>
+        <v>99.92401574878377</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.56163268129343</v>
+        <v>80.26874628275422</v>
       </c>
       <c r="C18" t="n">
-        <v>35.95016107763339</v>
+        <v>36.64439048857589</v>
       </c>
       <c r="D18" t="n">
-        <v>1.287742493671725</v>
+        <v>1.327064788801264</v>
       </c>
       <c r="E18" t="n">
-        <v>12.03537078865347</v>
+        <v>12.26199160202189</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580805737440111</v>
+        <v>0.7584810270450684</v>
       </c>
       <c r="G18" t="n">
-        <v>21.89451626406281</v>
+        <v>22.32580956345468</v>
       </c>
       <c r="H18" t="n">
-        <v>37.15163433532967</v>
+        <v>36.9520357149939</v>
       </c>
       <c r="I18" t="n">
-        <v>1.696284639931655</v>
+        <v>1.902857167405761</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738003585900069</v>
+        <v>4.740506419031674</v>
       </c>
       <c r="K18" t="n">
-        <v>20.43836731870658</v>
+        <v>19.73125371724578</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55496893761543</v>
+        <v>43.56097730377953</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94349733395541</v>
+        <v>99.9366215096012</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.61743682673405</v>
+        <v>79.31890537889541</v>
       </c>
       <c r="C19" t="n">
-        <v>35.26548619824769</v>
+        <v>35.98779179515936</v>
       </c>
       <c r="D19" t="n">
-        <v>1.253901139007007</v>
+        <v>1.292829415557947</v>
       </c>
       <c r="E19" t="n">
-        <v>11.95508457636201</v>
+        <v>12.21012095075244</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585357040001128</v>
+        <v>0.7589868065233023</v>
       </c>
       <c r="G19" t="n">
-        <v>21.31913718498005</v>
+        <v>21.74985243625631</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17393913172635</v>
+        <v>36.97667651769983</v>
       </c>
       <c r="I19" t="n">
-        <v>1.415990940657816</v>
+        <v>1.586771711334953</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740848150000705</v>
+        <v>4.743667540770637</v>
       </c>
       <c r="K19" t="n">
-        <v>21.38256317326595</v>
+        <v>20.68109462110457</v>
       </c>
       <c r="L19" t="n">
-        <v>43.30477925083291</v>
+        <v>43.27825644019704</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95282862234654</v>
+        <v>99.94714285646097</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.10759882082708</v>
+        <v>76.84227989782313</v>
       </c>
       <c r="C20" t="n">
-        <v>32.97348600686691</v>
+        <v>33.75554908792533</v>
       </c>
       <c r="D20" t="n">
-        <v>1.163356706735526</v>
+        <v>1.20269376116272</v>
       </c>
       <c r="E20" t="n">
-        <v>11.28857281585588</v>
+        <v>11.57934665953836</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589279246786899</v>
+        <v>0.7594224137916942</v>
       </c>
       <c r="G20" t="n">
-        <v>19.77967836092912</v>
+        <v>20.23345966335863</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19316088695124</v>
+        <v>36.99789863765455</v>
       </c>
       <c r="I20" t="n">
-        <v>1.180602596434826</v>
+        <v>1.323068676119088</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743299529241812</v>
+        <v>4.746390086198086</v>
       </c>
       <c r="K20" t="n">
-        <v>23.89240117917292</v>
+        <v>23.15772010217687</v>
       </c>
       <c r="L20" t="n">
-        <v>43.09477973227523</v>
+        <v>43.04265381791626</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96066691831506</v>
+        <v>99.95592300801846</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.82319651027339</v>
+        <v>82.73066518321689</v>
       </c>
       <c r="C21" t="n">
-        <v>36.54351019274363</v>
+        <v>37.30409533066975</v>
       </c>
       <c r="D21" t="n">
-        <v>1.164138838727751</v>
+        <v>1.203672747255033</v>
       </c>
       <c r="E21" t="n">
-        <v>13.21136934701732</v>
+        <v>13.5231507275343</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594381566705181</v>
+        <v>0.7600405794505684</v>
       </c>
       <c r="G21" t="n">
-        <v>21.43313228085712</v>
+        <v>21.84759660440806</v>
       </c>
       <c r="H21" t="n">
-        <v>38.85832200012513</v>
+        <v>38.62568173962313</v>
       </c>
       <c r="I21" t="n">
-        <v>1.650307407684836</v>
+        <v>2.020269163379757</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746488479190738</v>
+        <v>4.750253621566049</v>
       </c>
       <c r="K21" t="n">
-        <v>18.17680348972659</v>
+        <v>17.2693348167831</v>
       </c>
       <c r="L21" t="n">
-        <v>45.22471302949244</v>
+        <v>45.35928231878275</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94502671196267</v>
+        <v>99.93271246623561</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_74_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.58973163371944</v>
+        <v>44.01747346036932</v>
       </c>
       <c r="M2" t="n">
-        <v>98.91143993348561</v>
+        <v>96.3549761311036</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06061429070972</v>
+        <v>81.55022706481013</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94945385503286</v>
+        <v>43.30578262036568</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228800274374576</v>
+        <v>2.184426364256382</v>
       </c>
       <c r="E3" t="n">
-        <v>5.72000761511196</v>
+        <v>4.152991640368788</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429334247915254</v>
+        <v>0.7376846879157368</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9799900854966</v>
+        <v>32.85741322902308</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17493754041016</v>
+        <v>33.93349564412389</v>
       </c>
       <c r="I3" t="n">
-        <v>6.570611445577874</v>
+        <v>3.073686199648904</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643333904947033</v>
+        <v>4.610529299473355</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93938570929028</v>
+        <v>18.44977293518987</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87531655065502</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641561149782</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20985155342159</v>
+        <v>88.74677187766892</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73355358548342</v>
+        <v>42.94468277208258</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188155937218148</v>
+        <v>2.19020454630381</v>
       </c>
       <c r="E4" t="n">
-        <v>6.530196552420548</v>
+        <v>6.568650745030211</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444915325874595</v>
+        <v>0.7396359903217707</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36033197189798</v>
+        <v>33.55978753517633</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24661049902313</v>
+        <v>34.02325555480144</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486992981602683</v>
+        <v>7.042512566524288</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653072078671621</v>
+        <v>4.622724939511067</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79014844657844</v>
+        <v>11.25322812233109</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29378098333876</v>
+        <v>45.5679580035867</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81748301540061</v>
+        <v>99.76586889800035</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.10665498429458</v>
+        <v>87.76303097384179</v>
       </c>
       <c r="C5" t="n">
-        <v>42.48206178355309</v>
+        <v>43.05266465835562</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134566401878913</v>
+        <v>2.144070132010443</v>
       </c>
       <c r="E5" t="n">
-        <v>7.133700978959683</v>
+        <v>7.41060072637188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458116858990289</v>
+        <v>0.7412883351384199</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54331310284543</v>
+        <v>32.85288500209646</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30733755135533</v>
+        <v>34.0992634163673</v>
       </c>
       <c r="I5" t="n">
-        <v>4.580602226487262</v>
+        <v>5.881871267242162</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66132303686893</v>
+        <v>4.633052094615124</v>
       </c>
       <c r="K5" t="n">
-        <v>13.89334501570543</v>
+        <v>12.23696902615819</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47217672903032</v>
+        <v>44.51474096641608</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84758352828884</v>
+        <v>99.8043746509299</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.78898533084809</v>
+        <v>86.49579404112212</v>
       </c>
       <c r="C6" t="n">
-        <v>41.87591726981537</v>
+        <v>42.69853382779228</v>
       </c>
       <c r="D6" t="n">
-        <v>2.07040364047598</v>
+        <v>2.083936733079138</v>
       </c>
       <c r="E6" t="n">
-        <v>7.556420526485976</v>
+        <v>8.021232835712155</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469325734358179</v>
+        <v>0.7426912338693661</v>
       </c>
       <c r="G6" t="n">
-        <v>31.56509624716887</v>
+        <v>31.93148060847109</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35889837804762</v>
+        <v>34.16379675799082</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822905381259976</v>
+        <v>4.910835660316019</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668328583973861</v>
+        <v>4.641820211683537</v>
       </c>
       <c r="K6" t="n">
-        <v>15.2110146691519</v>
+        <v>13.50420595887786</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78582911029698</v>
+        <v>43.63387490035089</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87276104926426</v>
+        <v>99.83661468702104</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.37791365670429</v>
+        <v>84.97193896985949</v>
       </c>
       <c r="C7" t="n">
-        <v>41.05874039415338</v>
+        <v>41.93754684824631</v>
       </c>
       <c r="D7" t="n">
-        <v>2.002029656536116</v>
+        <v>2.011622127056861</v>
       </c>
       <c r="E7" t="n">
-        <v>7.838509923200354</v>
+        <v>8.42604558696441</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478850951894056</v>
+        <v>0.7438854513846941</v>
       </c>
       <c r="G7" t="n">
-        <v>30.5226756574485</v>
+        <v>30.82342756479845</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40271437871265</v>
+        <v>34.21873076369591</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189817100683479</v>
+        <v>4.098943404804825</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674281844933784</v>
+        <v>4.649284071154337</v>
       </c>
       <c r="K7" t="n">
-        <v>16.62208634329572</v>
+        <v>15.02806103014051</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2129814464048</v>
+        <v>42.89798001993771</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89380818385389</v>
+        <v>99.86358789832454</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.37096244791047</v>
+        <v>83.13359163454638</v>
       </c>
       <c r="C8" t="n">
-        <v>43.37239346210924</v>
+        <v>40.73593109000308</v>
       </c>
       <c r="D8" t="n">
-        <v>2.00636652314173</v>
+        <v>1.924632261678829</v>
       </c>
       <c r="E8" t="n">
-        <v>9.685338170442714</v>
+        <v>8.631751168370444</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495051900184577</v>
+        <v>0.7449056721495919</v>
       </c>
       <c r="G8" t="n">
-        <v>31.02513837293072</v>
+        <v>29.49051032438495</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47723874084905</v>
+        <v>34.26566091888121</v>
       </c>
       <c r="I8" t="n">
-        <v>5.742968012912427</v>
+        <v>3.420470838146415</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68440743761536</v>
+        <v>4.655660450934948</v>
       </c>
       <c r="K8" t="n">
-        <v>11.62903755208954</v>
+        <v>16.86640836545363</v>
       </c>
       <c r="L8" t="n">
-        <v>44.80755050960268</v>
+        <v>42.28380100552093</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80898152380146</v>
+        <v>99.88614046097763</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.56896786540942</v>
+        <v>81.10799596333935</v>
       </c>
       <c r="C9" t="n">
-        <v>42.46198812027041</v>
+        <v>39.24126914956376</v>
       </c>
       <c r="D9" t="n">
-        <v>1.925276522765515</v>
+        <v>1.829426280282398</v>
       </c>
       <c r="E9" t="n">
-        <v>10.09299922584513</v>
+        <v>8.680386005474759</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508889072383336</v>
+        <v>0.7457793071996096</v>
       </c>
       <c r="G9" t="n">
-        <v>29.77121569563566</v>
+        <v>28.03170022688323</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54088973296334</v>
+        <v>34.30584813118202</v>
       </c>
       <c r="I9" t="n">
-        <v>4.794642110721873</v>
+        <v>2.853735342319766</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693055670239584</v>
+        <v>4.661120669997558</v>
       </c>
       <c r="K9" t="n">
-        <v>13.43103213459058</v>
+        <v>18.89200403666067</v>
       </c>
       <c r="L9" t="n">
-        <v>43.94745285589144</v>
+        <v>41.77171373493817</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84047311075243</v>
+        <v>99.90498692116259</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.59574166264551</v>
+        <v>85.87851156968276</v>
       </c>
       <c r="C10" t="n">
-        <v>41.23307666409875</v>
+        <v>42.48596859546242</v>
       </c>
       <c r="D10" t="n">
-        <v>1.837260873057303</v>
+        <v>1.831541208915002</v>
       </c>
       <c r="E10" t="n">
-        <v>10.2985617760797</v>
+        <v>10.53981040833521</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520729439208435</v>
+        <v>0.7466414736762804</v>
       </c>
       <c r="G10" t="n">
-        <v>28.41019931119921</v>
+        <v>29.41709188185865</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59535542035879</v>
+        <v>35.69849308474127</v>
       </c>
       <c r="I10" t="n">
-        <v>4.001835438524374</v>
+        <v>2.978424301679598</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70045589950527</v>
+        <v>4.66650921047675</v>
       </c>
       <c r="K10" t="n">
-        <v>15.4042583373545</v>
+        <v>14.12148843031725</v>
       </c>
       <c r="L10" t="n">
-        <v>43.22948049547115</v>
+        <v>43.29337680631756</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8668154969244</v>
+        <v>99.90083383209722</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.44975981595643</v>
+        <v>85.46925040421338</v>
       </c>
       <c r="C11" t="n">
-        <v>39.70792353514082</v>
+        <v>42.45268499012926</v>
       </c>
       <c r="D11" t="n">
-        <v>1.74236918411664</v>
+        <v>1.807755365736726</v>
       </c>
       <c r="E11" t="n">
-        <v>10.32321780787109</v>
+        <v>10.86448587275104</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530882879604626</v>
+        <v>0.7473781782221669</v>
       </c>
       <c r="G11" t="n">
-        <v>26.94285635772171</v>
+        <v>29.07495326265165</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64206124618127</v>
+        <v>35.77361148204199</v>
       </c>
       <c r="I11" t="n">
-        <v>3.33936513235236</v>
+        <v>2.529952628921271</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706801799752889</v>
+        <v>4.671113613888541</v>
       </c>
       <c r="K11" t="n">
-        <v>17.55024018404357</v>
+        <v>14.53074959578661</v>
       </c>
       <c r="L11" t="n">
-        <v>42.63067418530105</v>
+        <v>42.93231678716265</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88883790448544</v>
+        <v>99.91575137307852</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.06965951090092</v>
+        <v>83.53937985459019</v>
       </c>
       <c r="C12" t="n">
-        <v>37.84523204544111</v>
+        <v>40.91608443931082</v>
       </c>
       <c r="D12" t="n">
-        <v>1.637956083067075</v>
+        <v>1.725638935189584</v>
       </c>
       <c r="E12" t="n">
-        <v>10.16892798287378</v>
+        <v>10.72264990657657</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539617473907135</v>
+        <v>0.7480074301482411</v>
       </c>
       <c r="G12" t="n">
-        <v>25.32828052093144</v>
+        <v>27.7542372932755</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68224037997282</v>
+        <v>35.80373092435867</v>
       </c>
       <c r="I12" t="n">
-        <v>2.786031875473134</v>
+        <v>2.110068926615134</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712260921191958</v>
+        <v>4.675046438426505</v>
       </c>
       <c r="K12" t="n">
-        <v>19.93034048909908</v>
+        <v>16.46062014540978</v>
       </c>
       <c r="L12" t="n">
-        <v>42.13166732289446</v>
+        <v>42.55301895336493</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90723985743465</v>
+        <v>99.92972353808554</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.67692016506126</v>
+        <v>84.72061869233997</v>
       </c>
       <c r="C13" t="n">
-        <v>35.88333586001684</v>
+        <v>41.90046181181307</v>
       </c>
       <c r="D13" t="n">
-        <v>1.533945524215433</v>
+        <v>1.726973870115952</v>
       </c>
       <c r="E13" t="n">
-        <v>9.910533672618266</v>
+        <v>11.37012367960669</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547136711353766</v>
+        <v>0.7485860803069303</v>
       </c>
       <c r="G13" t="n">
-        <v>23.71992933315094</v>
+        <v>28.0871919091067</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71682887222732</v>
+        <v>36.14291253818381</v>
       </c>
       <c r="I13" t="n">
-        <v>2.324008647117833</v>
+        <v>1.966167613101569</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716960444596102</v>
+        <v>4.678663001918312</v>
       </c>
       <c r="K13" t="n">
-        <v>22.32307983493873</v>
+        <v>15.27938130766002</v>
       </c>
       <c r="L13" t="n">
-        <v>41.71619453072572</v>
+        <v>42.75466862107321</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9226102256813</v>
+        <v>99.9345117405463</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.18329835632866</v>
+        <v>82.75122298014385</v>
       </c>
       <c r="C14" t="n">
-        <v>39.76899256506196</v>
+        <v>40.23655866209313</v>
       </c>
       <c r="D14" t="n">
-        <v>1.535901603431192</v>
+        <v>1.645477545951806</v>
       </c>
       <c r="E14" t="n">
-        <v>12.11893662338747</v>
+        <v>11.10682391641215</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755676078015316</v>
+        <v>0.7490804730558256</v>
       </c>
       <c r="G14" t="n">
-        <v>25.40919146911327</v>
+        <v>26.76175037446932</v>
       </c>
       <c r="H14" t="n">
-        <v>36.42011419629289</v>
+        <v>36.16678259715621</v>
       </c>
       <c r="I14" t="n">
-        <v>3.220502898492804</v>
+        <v>1.639555116499641</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722975487595723</v>
+        <v>4.681752956598908</v>
       </c>
       <c r="K14" t="n">
-        <v>15.81670164367134</v>
+        <v>17.24877701985617</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30709241258347</v>
+        <v>42.4600485510201</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89278662131676</v>
+        <v>99.94538423296939</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.41525749234228</v>
+        <v>81.91239810668128</v>
       </c>
       <c r="C15" t="n">
-        <v>39.49005580001082</v>
+        <v>39.6296796652037</v>
       </c>
       <c r="D15" t="n">
-        <v>1.506269601344428</v>
+        <v>1.610375496968991</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34181015992635</v>
+        <v>11.10133881879794</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564873703649724</v>
+        <v>0.7495037913484439</v>
       </c>
       <c r="G15" t="n">
-        <v>24.92788511453782</v>
+        <v>26.1908569734493</v>
       </c>
       <c r="H15" t="n">
-        <v>36.46812549466731</v>
+        <v>36.18722106966914</v>
       </c>
       <c r="I15" t="n">
-        <v>2.686633686720347</v>
+        <v>1.388703260519685</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728046064781075</v>
+        <v>4.684398695927773</v>
       </c>
       <c r="K15" t="n">
-        <v>16.58474250765771</v>
+        <v>18.08760189331873</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83574327848446</v>
+        <v>42.23645447735752</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91054158615299</v>
+        <v>99.95373603587993</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.9741418257326</v>
+        <v>79.65041212618847</v>
       </c>
       <c r="C16" t="n">
-        <v>37.46448014716393</v>
+        <v>37.58296455292182</v>
       </c>
       <c r="D16" t="n">
-        <v>1.412745415125774</v>
+        <v>1.517475301233099</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94899571932394</v>
+        <v>10.65388780604757</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571852197966021</v>
+        <v>0.7498669556429808</v>
       </c>
       <c r="G16" t="n">
-        <v>23.38011427231383</v>
+        <v>24.6799449259773</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50176685028806</v>
+        <v>36.2047552126084</v>
       </c>
       <c r="I16" t="n">
-        <v>2.240926725155647</v>
+        <v>1.157813451910498</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73240762372876</v>
+        <v>4.686668472768629</v>
       </c>
       <c r="K16" t="n">
-        <v>19.0258581742674</v>
+        <v>20.34958787381154</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43503296504867</v>
+        <v>42.02887248269666</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92537128647999</v>
+        <v>99.96142490943001</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.63006549596273</v>
+        <v>84.48271177116985</v>
       </c>
       <c r="C17" t="n">
-        <v>38.65324011704205</v>
+        <v>40.74935041055319</v>
       </c>
       <c r="D17" t="n">
-        <v>1.414045731244722</v>
+        <v>1.518274777423717</v>
       </c>
       <c r="E17" t="n">
-        <v>12.727760177807</v>
+        <v>12.34569128238879</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578821466001077</v>
+        <v>0.7502620202457986</v>
       </c>
       <c r="G17" t="n">
-        <v>23.78912919413871</v>
+        <v>26.15659097345066</v>
       </c>
       <c r="H17" t="n">
-        <v>36.9228591755656</v>
+        <v>37.68747306330523</v>
       </c>
       <c r="I17" t="n">
-        <v>2.28162565435592</v>
+        <v>1.335282027819423</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73676341625067</v>
+        <v>4.68913762653624</v>
       </c>
       <c r="K17" t="n">
-        <v>17.36993450403726</v>
+        <v>15.51728822883015</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90084112770447</v>
+        <v>43.68887539695304</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92401574878377</v>
+        <v>99.95551403633638</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.26874628275422</v>
+        <v>86.17780717479943</v>
       </c>
       <c r="C18" t="n">
-        <v>36.64439048857589</v>
+        <v>41.48687195936643</v>
       </c>
       <c r="D18" t="n">
-        <v>1.327064788801264</v>
+        <v>1.519591195670575</v>
       </c>
       <c r="E18" t="n">
-        <v>12.26199160202189</v>
+        <v>12.95871203754418</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584810270450684</v>
+        <v>0.7509125339920996</v>
       </c>
       <c r="G18" t="n">
-        <v>22.32580956345468</v>
+        <v>26.29362733260429</v>
       </c>
       <c r="H18" t="n">
-        <v>36.9520357149939</v>
+        <v>37.72014993968902</v>
       </c>
       <c r="I18" t="n">
-        <v>1.902857167405761</v>
+        <v>2.241610797848635</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740506419031674</v>
+        <v>4.693203337450622</v>
       </c>
       <c r="K18" t="n">
-        <v>19.73125371724578</v>
+        <v>13.82219282520057</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56097730377953</v>
+        <v>44.61627958557521</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9366215096012</v>
+        <v>99.92534437014223</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.31890537889541</v>
+        <v>83.59642921368398</v>
       </c>
       <c r="C19" t="n">
-        <v>35.98779179515936</v>
+        <v>39.25279997173025</v>
       </c>
       <c r="D19" t="n">
-        <v>1.292829415557947</v>
+        <v>1.424442886865968</v>
       </c>
       <c r="E19" t="n">
-        <v>12.21012095075244</v>
+        <v>12.45887681064775</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589868065233023</v>
+        <v>0.7514722696070985</v>
       </c>
       <c r="G19" t="n">
-        <v>21.74985243625631</v>
+        <v>24.64726732462078</v>
       </c>
       <c r="H19" t="n">
-        <v>36.97667651769983</v>
+        <v>37.74826681131999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.586771711334953</v>
+        <v>1.869401425578032</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743667540770637</v>
+        <v>4.696701685044365</v>
       </c>
       <c r="K19" t="n">
-        <v>20.68109462110457</v>
+        <v>16.403570786316</v>
       </c>
       <c r="L19" t="n">
-        <v>43.27825644019704</v>
+        <v>44.28136227534684</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94714285646097</v>
+        <v>99.9377330333931</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.84227989782313</v>
+        <v>80.87326724912123</v>
       </c>
       <c r="C20" t="n">
-        <v>33.75554908792533</v>
+        <v>36.81853641406467</v>
       </c>
       <c r="D20" t="n">
-        <v>1.20269376116272</v>
+        <v>1.324620439258527</v>
       </c>
       <c r="E20" t="n">
-        <v>11.57934665953836</v>
+        <v>11.8455865819535</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7594224137916942</v>
+        <v>0.7519550915332696</v>
       </c>
       <c r="G20" t="n">
-        <v>20.23345966335863</v>
+        <v>22.92003025961513</v>
       </c>
       <c r="H20" t="n">
-        <v>36.99789863765455</v>
+        <v>37.77252012262447</v>
       </c>
       <c r="I20" t="n">
-        <v>1.323068676119088</v>
+        <v>1.558835432053397</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746390086198086</v>
+        <v>4.699719322082935</v>
       </c>
       <c r="K20" t="n">
-        <v>23.15772010217687</v>
+        <v>19.12673275087876</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04265381791626</v>
+        <v>44.00280301767939</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95592300801846</v>
+        <v>99.94807218262282</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.73066518321689</v>
+        <v>78.23351456951127</v>
       </c>
       <c r="C21" t="n">
-        <v>37.30409533066975</v>
+        <v>34.418944613869</v>
       </c>
       <c r="D21" t="n">
-        <v>1.203672747255033</v>
+        <v>1.228413469963694</v>
       </c>
       <c r="E21" t="n">
-        <v>13.5231507275343</v>
+        <v>11.20186835460079</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7600405794505684</v>
+        <v>0.7523715169919353</v>
       </c>
       <c r="G21" t="n">
-        <v>21.84759660440806</v>
+        <v>21.25535215102596</v>
       </c>
       <c r="H21" t="n">
-        <v>38.62568173962313</v>
+        <v>37.79343817902721</v>
       </c>
       <c r="I21" t="n">
-        <v>2.020269163379757</v>
+        <v>1.299748916702099</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750253621566049</v>
+        <v>4.702321981199595</v>
       </c>
       <c r="K21" t="n">
-        <v>17.2693348167831</v>
+        <v>21.76648543048871</v>
       </c>
       <c r="L21" t="n">
-        <v>45.35928231878275</v>
+        <v>43.77126897141857</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93271246623561</v>
+        <v>99.95669901577629</v>
       </c>
     </row>
   </sheetData>
